--- a/utils/data-room-simulator/output/fixed_assets.xlsx
+++ b/utils/data-room-simulator/output/fixed_assets.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fixed Assets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>beginning_gross</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>additions</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>disposals</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ending_gross</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>beginning_accum_depr</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>depreciation_expense</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ending_accum_depr</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>net_fixed_assets</t>
         </is>
@@ -480,28 +468,28 @@
         <v>2021</v>
       </c>
       <c r="B2" t="n">
-        <v>5673305.56</v>
+        <v>3120818.59</v>
       </c>
       <c r="C2" t="n">
-        <v>630367.28</v>
+        <v>346757.62</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>6303672.84</v>
+        <v>3467576.21</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>372020.04</v>
+        <v>201343.13</v>
       </c>
       <c r="H2" t="n">
-        <v>372020.04</v>
+        <v>201343.13</v>
       </c>
       <c r="I2" t="n">
-        <v>5931652.8</v>
+        <v>3266233.08</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2022</v>
       </c>
       <c r="B3" t="n">
-        <v>6303672.84</v>
+        <v>3467576.21</v>
       </c>
       <c r="C3" t="n">
-        <v>148031.45</v>
+        <v>81430.36</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>6451704.29</v>
+        <v>3549006.57</v>
       </c>
       <c r="F3" t="n">
-        <v>372020.04</v>
+        <v>201343.13</v>
       </c>
       <c r="G3" t="n">
-        <v>389492.6</v>
+        <v>210799.57</v>
       </c>
       <c r="H3" t="n">
-        <v>761512.64</v>
+        <v>412142.7</v>
       </c>
       <c r="I3" t="n">
-        <v>5690191.65</v>
+        <v>3136863.87</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>6451704.29</v>
+        <v>3549006.57</v>
       </c>
       <c r="C4" t="n">
-        <v>148031.46</v>
+        <v>81430.36</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>6599735.75</v>
+        <v>3630436.93</v>
       </c>
       <c r="F4" t="n">
-        <v>761512.64</v>
+        <v>412142.7</v>
       </c>
       <c r="G4" t="n">
-        <v>406965.16</v>
+        <v>220255.99</v>
       </c>
       <c r="H4" t="n">
-        <v>1168477.8</v>
+        <v>632398.6899999999</v>
       </c>
       <c r="I4" t="n">
-        <v>5431257.95</v>
+        <v>2998038.24</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>2024</v>
       </c>
       <c r="B5" t="n">
-        <v>6599735.75</v>
+        <v>3630436.93</v>
       </c>
       <c r="C5" t="n">
-        <v>148031.45</v>
+        <v>81430.36</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6747767.2</v>
+        <v>3711867.29</v>
       </c>
       <c r="F5" t="n">
-        <v>1168477.8</v>
+        <v>632398.6899999999</v>
       </c>
       <c r="G5" t="n">
-        <v>424437.74</v>
+        <v>229712.42</v>
       </c>
       <c r="H5" t="n">
-        <v>1592915.54</v>
+        <v>862111.11</v>
       </c>
       <c r="I5" t="n">
-        <v>5154851.66</v>
+        <v>2849756.18</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>2025</v>
       </c>
       <c r="B6" t="n">
-        <v>6747767.2</v>
+        <v>3711867.29</v>
       </c>
       <c r="C6" t="n">
-        <v>148031.46</v>
+        <v>81430.37</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>6895798.66</v>
+        <v>3793297.66</v>
       </c>
       <c r="F6" t="n">
-        <v>1592915.54</v>
+        <v>862111.11</v>
       </c>
       <c r="G6" t="n">
-        <v>441910.29</v>
+        <v>239168.85</v>
       </c>
       <c r="H6" t="n">
-        <v>2034825.83</v>
+        <v>1101279.96</v>
       </c>
       <c r="I6" t="n">
-        <v>4860972.83</v>
+        <v>2692017.7</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>6895798.66</v>
+        <v>3793297.66</v>
       </c>
       <c r="C7" t="n">
-        <v>12335.95</v>
+        <v>13571.72</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>6908134.61</v>
+        <v>3806869.38</v>
       </c>
       <c r="F7" t="n">
-        <v>2034825.83</v>
+        <v>1101279.96</v>
       </c>
       <c r="G7" t="n">
-        <v>37614.55</v>
+        <v>40780.85</v>
       </c>
       <c r="H7" t="n">
-        <v>2072440.38</v>
+        <v>1142060.81</v>
       </c>
       <c r="I7" t="n">
-        <v>4835694.23</v>
+        <v>2664808.57</v>
       </c>
     </row>
   </sheetData>
